--- a/templates/000_pm_suite/02_프로젝트 개발/03_분석/03_요구사항정의/프로젝트명_요구사항정의서_V1.0_20230530.xlsx
+++ b/templates/000_pm_suite/02_프로젝트 개발/03_분석/03_요구사항정의/프로젝트명_요구사항정의서_V1.0_20230530.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\00. 엠파시\08. 프로젝트\010. 진행중\한빛글로벌\syncguard_ai\2.분석 (Analysis)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\00. 엠파시\08. 프로젝트\010. 진행중\한빛글로벌\syncflow_ai\2.분석 (Analysis)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5903CC-9F5E-460F-B739-F795C1C1A7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -97,10 +97,10 @@
     <t>요구사항정의서</t>
   </si>
   <si>
-    <t>한빛글로벌 SyncGuard AI</t>
-  </si>
-  <si>
-    <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+    <t>한빛글로벌 SyncFlow AI</t>
+  </si>
+  <si>
+    <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
   </si>
   <si>
     <t>최종작성일</t>
@@ -157,13 +157,13 @@
     <t>초기 제정</t>
   </si>
   <si>
-    <t>SyncGuard AI 착수보고서(v1.8) 및 킥오프 회의 합의사항(동영상 캡처, 마케팅허브/프로덕트랩 연계, AWS EC2) 반영</t>
+    <t>SyncFlow AI 착수보고서(v1.8) 및 킥오프 회의 합의사항(동도면 스냅샷, 전자구매포털/피엘엠넥서스 연계, AWS EC2) 반영</t>
   </si>
   <si>
     <t>엠파시</t>
   </si>
   <si>
-    <t>한빛글로벌 RA</t>
+    <t>한빛글로벌 QA</t>
   </si>
   <si>
     <t>개정 사유   제정 또는 개정 내용이 이전 문서에 대해 추가/수정/삭제인지 선택 기입</t>
@@ -244,14 +244,14 @@
     <t>데이터 처리</t>
   </si>
   <si>
-    <t>[F-01] 문서 및 동영상 장면 파싱</t>
-  </si>
-  <si>
-    <t>PPTX, PDF, 긴 상세페이지(JPG/PNG) 및 동영상(MP4) 재생 중 사용자가 지정한 캡처 장면 이미지를 구조적으로 분해하여 텍스트·타임스탬프·레이아웃 정보를 추출합니다.
+    <t>[F-01] 문서 및 설계도면 장면 파싱</t>
+  </si>
+  <si>
+    <t>PPTX, PDF, 다단 기술시방서(PDF/TIFF) 및 설계도면(CAD/PDF) 재생 중 사용자가 지정한 도면 스냅샷 이미지를 구조적으로 분해하여 텍스트·타임스탬프·레이아웃 정보를 추출합니다.
 [처리절차]
 1. PPTX/PDF: 슬라이드·페이지별 텍스트 박스, 표(Table), 도형 텍스트 및 좌표 추출
-2. 동영상(MP4): 내장 플레이어에서 사용자가 직접 지정·캡처한 다중 스냅샷 이미지(프레임 타임스탬프 매핑) 저장 및 일괄 분석 전달
-3. 긴 상세페이지(JPG): 세로 분할(Slicing) 및 문맥 유지 전처리 수행
+2. 설계도면(CAD/PDF): 내장 플레이어에서 사용자가 직접 지정·스냅샷한 다중 스냅샷 이미지(프레임 타임스탬프 매핑) 저장 및 일괄 분석 전달
+3. 다단 기술시방서(PDF/TIFF): 세로 분할(Slicing) 및 문맥 유지 전처리 수행
 [출력] 슬라이드/장면별 구조화 JSON 및 이미지 스냅샷 메타데이터</t>
   </si>
   <si>
@@ -264,7 +264,7 @@
     <t>기능</t>
   </si>
   <si>
-    <t>제품 표시·광고 관리 가이드라인 준수</t>
+    <t>구매계약·기술규격 관리 가이드라인 준수</t>
   </si>
   <si>
     <t>AWS EC2 + Spring Boot 3 + 비학습 LLM·하이브리드 RAG 적용</t>
@@ -276,26 +276,26 @@
     <t>[F-02] 멀티모달 OCR 텍스트 추출</t>
   </si>
   <si>
-    <t>시안 내 이미지, 긴 상세페이지(JPG/PNG), 스캔본 PDF 및 동영상 사용자 지정 캡처 스냅샷 이미지에서 국문/영문 혼용 텍스트와 바운딩 박스 좌표를 추출합니다.
+    <t>계약·도서 내 이미지, 다단 기술시방서(PDF/TIFF), 스캔본 PDF 및 설계도면 사용자 지정 스냅샷 스냅샷 이미지에서 국문/영문 혼용 텍스트와 바운딩 박스 좌표를 추출합니다.
 [처리절차]
-1. 이미지 전처리 (해상도 정규화, 대비 보정, 동영상 전환 구간 노이즈 배제)
+1. 이미지 전처리 (해상도 정규화, 대비 보정, 설계도면 전환 구간 노이즈 배제)
 2. Vision OCR 엔진을 통한 텍스트 및 상대 좌표(%) 추출
-3. 국·영문 혼용 광고 문구의 자동 번역 연계 및 저신뢰 구간 수동 편집 지원
-[출력] 문장별 추출 텍스트, 신뢰도 점수, 시안/스냅샷 내 바운딩 박스 좌표</t>
+3. 국·영문 혼용 구매계약 조항의 자동 번역 연계 및 저신뢰 구간 수동 편집 지원
+[출력] 문장별 추출 텍스트, 신뢰도 점수, 계약·도서/스냅샷 내 바운딩 박스 좌표</t>
   </si>
   <si>
     <t>[F-03] 문장 분리 및 정제</t>
   </si>
   <si>
-    <t>추출된 원문 텍스트를 심의 가능한 개별 광고 문구 문장 단위로 분리하고 각주 및 메타정보를 결합합니다.
-[처리절차] 1. 한국어 문장 분리기(KSS/정규식)를 적용하여 종결 어미, 줄바꿈, 특수기호 기반 분리. 2. 주석 기호(`*`, `※`, `†`, `1)`)와 하단 각주(Footnote) 텍스트를 탐색하여 해당 문장과 양방향 링크 매핑. 3. 브랜드명, 법인명, 전성분 단순 나열, 바코드 번호 등 비검토 대상 텍스트 자동 필터링 및 분류. 4. 동일 슬라이드 내 중복 문장 병합 및 슬라이드-문장 위치 좌표 매핑.
-[출력] 슬라이드 번호, 문장 고유키, 원문 텍스트, 연결 각주, 바운딩 박스 정보를 가진 문장 엔티티 리스트.</t>
+    <t>추출된 원문 텍스트를 검증 가능한 개별 구매계약 조항 문장 단위로 분리하고 특약주석 및 메타정보를 결합합니다.
+[처리절차] 1. 한국어 문장 분리기(KSS/정규식)를 적용하여 종결 어미, 줄바꿈, 특수기호 기반 분리. 2. 주석 기호(`*`, `※`, `†`, `1)`)와 하단 특약주석(Footnote) 텍스트를 탐색하여 해당 문장과 양방향 링크 매핑. 3. 사업본부명, 법인명, 자재BOM 단순 나열, 바코드 번호 등 비검토 대상 텍스트 자동 필터링 및 분류. 4. 동일 슬라이드 내 중복 문장 병합 및 슬라이드-문장 위치 좌표 매핑.
+[출력] 슬라이드 번호, 문장 고유키, 원문 텍스트, 연결 특약주석, 바운딩 박스 정보를 가진 문장 엔티티 리스트.</t>
   </si>
   <si>
     <t>[F-04] 국내 규제 문서 수집 및 적재</t>
   </si>
   <si>
-    <t>식약처 제품 표시·광고 관리 지침, 질의응답집, 서울식약청 위반 사례집 등 규제 문서를 체계적으로 적재합니다.
+    <t>공정위·표준원 구매계약·기술규격 관리 지침, 질의응답집, 서울식약청 위반 사례집 등 규제 문서를 체계적으로 적재합니다.
 [처리절차] 1. HWP/PDF 문서 파싱 및 조항(제N조, 별표, [사례]) 단위 의미론적 청킹(Semantic Chunking). 2. 메타데이터 태깅 (문서명, 소관부처, 제정/개정일자, 관련 법 조항 번호, 규제 분류 코드). 3. 청크별 고유 식별자(Chunk ID) 부여 및 버전 관리.
 [출력] 구조화된 규제 조항 청크 데이터베이스 레코드.</t>
   </si>
@@ -303,9 +303,9 @@
     <t>[F-05] 표현 사전 구축</t>
   </si>
   <si>
-    <t>식약처 지침 및 과거 위반 사례를 바탕으로 표현 사전을 구축하고 자동/수동 승인 파이프라인을 운영합니다.
-[처리절차] 1. LLM 보조를 활용하여 규제 텍스트에서 금지/주의 표현 키워드 및 패턴 자동 1차 추출. 2. 등급(금지: PROHIBITED, 주의: CAUTION, 조건부허용: CONDITIONAL, 허용: ALLOWED) 부여. 3. 5대 카테고리 태깅 및 근거 법률 조항 매핑. 4. RA 전문가의 웹 UI 검수 및 최종 승인 시 룰 엔진 반영.
-[출력] 승인된 표현 사전 마스터 테이블 (`review_rule_dict`).</t>
+    <t>공정위·표준원 지침 및 과거 위반 사례를 바탕으로 표현 사전을 구축하고 자동/수동 승인 파이프라인을 운영합니다.
+[처리절차] 1. LLM 보조를 활용하여 규제 텍스트에서 금지/주의 표현 키워드 및 패턴 자동 1차 추출. 2. 등급(금지: PROHIBITED, 주의: CAUTION, 조건부허용: CONDITIONAL, 허용: ALLOWED) 부여. 3. 5대 카테고리 태깅 및 근거 법률 조항 매핑. 4. 법무·QA 전문위원의 웹 UI 검수 및 최종 승인 시 룰 엔진 반영.
+[출력] 승인된 표현 사전 마스터 테이블 (`verify_rule_dict`).</t>
   </si>
   <si>
     <t>[F-06] 데이터 임베딩 및 인덱싱</t>
@@ -322,8 +322,8 @@
     <t>[F-07] 규제 근거 하이브리드 검색</t>
   </si>
   <si>
-    <t>심의 대상 문장과 의미론적/키워드적으로 가장 관련 있는 규제 조항 및 유사 판정 사례를 고속 검색합니다.
-[처리절차] 1. Dense Vector 유사도 검색 (Cosine Similarity Top-K). 2. Sparse Keyword 검색 (BM25 / TF-IDF Top-K). 3. RRF(Reciprocal Rank Fusion) 알고리즘으로 점수 결합 및 Re-ranking. 4. 식약처 공식 조항, 한빛글로벌 과거 내부 심의 이력, 경쟁사 위반 사례 동시 검색.
+    <t>검증 대상 문장과 의미론적/키워드적으로 가장 관련 있는 규제 조항 및 유사 판정 사례를 고속 검색합니다.
+[처리절차] 1. Dense Vector 유사도 검색 (Cosine Similarity Top-K). 2. Sparse Keyword 검색 (BM25 / TF-IDF Top-K). 3. RRF(Reciprocal Rank Fusion) 알고리즘으로 점수 결합 및 Re-ranking. 4. 공정위·표준원 공식 조항, 한빛글로벌 과거 내부 검증 이력, 경쟁사 위반 사례 동시 검색.
 [출력] 유사도 점수와 출처 메타정보가 포함된 상위 3~5개 근거 청크.</t>
   </si>
   <si>
@@ -338,9 +338,9 @@
     <t>[F-09] 유사 사례 기반 신규 표현 검토</t>
   </si>
   <si>
-    <t>과거 심의 완료된 이력 DB에서 동일 또는 유사 문장의 최종 RA 판정을 검색하여 일관성을 보장합니다.
-[처리절차] 1. 문장 정규화 키(특수문자/공백 제거 해시)로 완전 일치 문장 탐색. 2. 벡터 코사인 유사도 95% 이상 문장 탐색. 3. 과거 판정(승인/반려/수정) 내역 및 확정 Claim을 프롬프트 Few-shot 컨텍스트에 최우선 주입. 4. UI 상에 "과거 동일/유사 판정 사례 존재" 배지 표시.
-[출력] 과거 심의 일자, 당시 판정 등급, 확정 Claim, 심의자 코멘트.</t>
+    <t>과거 검증 완료된 이력 DB에서 동일 또는 유사 문장의 최종 법무·QA 판정을 검색하여 일관성을 보장합니다.
+[처리절차] 1. 문장 정규화 키(특수문자/공백 제거 해시)로 완전 일치 문장 탐색. 2. 벡터 코사인 유사도 95% 이상 문장 탐색. 3. 과거 판정(승인/반려/수정) 내역 및 확정 Spec을 프롬프트 Few-shot 컨텍스트에 최우선 주입. 4. UI 상에 "과거 동일/유사 판정 사례 존재" 배지 표시.
+[출력] 과거 검증 일자, 당시 판정 등급, 확정 Spec, 검증자 코멘트.</t>
   </si>
   <si>
     <t>LLM 개발</t>
@@ -359,31 +359,31 @@
   <si>
     <t>룰 결과, RAG 근거, 문맥을 종합하여 안전/주의/금지 3단계 등급을 판정합니다.
 [처리절차] 1. LLM 체인 실행 및 JSON Structured Output 호출. 2. **No-Downgrade 핵심 규칙**: 룰 엔진에서 `금지(PROHIBITED)`로 매칭된 경우, LLM이 문맥상 안전하다고 보더라도 최종 등급을 `주의` 또는 `안전`으로 하향할 수 없음 (보수적 규제 안전성 확보). 3. 등급(SAFE, CAUTION, PROHIBITED), 상세 사유, 신뢰도 점수(0.0~1.0) 산출. 4. 프롬프트 버전 및 사용 모델 메타 기록.
-[출력] `SyncGuardAnalysis` JSON 결과.</t>
+[출력] `SyncFlowAnalysis` JSON 결과.</t>
   </si>
   <si>
     <t>[F-12] 대체 표현 권장 수정안 생성</t>
   </si>
   <si>
-    <t>주의/금지 판정을 받은 문장에 대해 규제를 준수하면서 마케팅 소구를 유지하는 대체 표현을 2~3개 제안합니다.
-[처리절차] 1. 승인 표현 DB(`review_rule_dict` 중 ALLOWED)에서 매칭되는 표준 표현 우선 검색 및 추천. 2. 부족분은 LLM을 통해 뉘앙스별(예: 효능 강조형, 안전 표현형, 감성 소구형) 2~3개 생성. 3. 생성된 대체 표현을 룰 엔진에 재입력하여 위반 여부 자동 검증 (재금지 시 자동 재생성). 4. 제안별 준수 사유 및 마케팅 뉘앙스 설명 생성.
-[출력] 권장 대체 문구 리스트 (문구 텍스트, 설명, 신뢰도).</t>
-  </si>
-  <si>
-    <t>[F-13] 실증자료 필요 여부 판단</t>
-  </si>
-  <si>
-    <t>문장 내 효능·효과 소구 표현에 대해 법적 실증자료(시험성적서/임상결과)가 필요한지 분류합니다.
-[처리절차] 1. 소구 유형 분류: 수치 표현(예: 99.9% 개선), 임상 효능(예: 모공 수 축소), 기능성 인증, 비교 우위. 2. 필요 실증 유형 도출: 3. 불확실하거나 모호한 경우 '실증자료 필요(REQUIRED)'로 보수적 판정.
-[출력] 실증 필요 여부(REQUIRED / NOT_REQUIRED), 권장 실증 유형, 실증 가이드 메모.</t>
+    <t>주의/금지 판정을 받은 문장에 대해 규제를 준수하면서 구매조달 기술사양를 유지하는 대체 표현을 2~3개 제안합니다.
+[처리절차] 1. 승인 표현 DB(`verify_rule_dict` 중 ALLOWED)에서 매칭되는 표준 표현 우선 검색 및 추천. 2. 부족분은 LLM을 통해 뉘앙스별(예: 성능규격 강조형, 안전 표현형, 감성 기술사양형) 2~3개 생성. 3. 생성된 대체 표현을 룰 엔진에 재입력하여 위반 여부 자동 검증 (재금지 시 자동 재생성). 4. 제안별 준수 사유 및 구매조달 뉘앙스 설명 생성.
+[출력] 권장 대체 조항 리스트 (조항 텍스트, 설명, 신뢰도).</t>
+  </si>
+  <si>
+    <t>[F-13] 시험성적서 필요 여부 판단</t>
+  </si>
+  <si>
+    <t>문장 내 성능·규격 기술사양 표현에 대해 법적 시험성적서(시험성적서/신뢰성결과)가 필요한지 분류합니다.
+[처리절차] 1. 기술사양 유형 분류: 수치 표현(예: 99.9% 개선), 신뢰성 성능규격(예: 불량률 PPM 감축), 핵심규격 인증, 비교 우위. 2. 필요 시험검증 유형 도출: 3. 불확실하거나 모호한 경우 '시험성적서 필요(REQUIRED)'로 보수적 판정.
+[출력] 시험검증 필요 여부(REQUIRED / NOT_REQUIRED), 권장 시험검증 유형, 시험검증 가이드 메모.</t>
   </si>
   <si>
     <t>[F-14] 프롬프트 및 체인 관리</t>
   </si>
   <si>
-    <t>판정, 대체문구 생성, 실증 분석, 동영상 스냅샷 문맥 분석 등 단계별 프롬프트 템플릿의 버전, 파라미터, 변수를 관리합니다.
+    <t>판정, 표준수정조항 생성, 시험검증 분석, 설계도면 스냅샷 문맥 분석 등 단계별 프롬프트 템플릿의 버전, 파라미터, 변수를 관리합니다.
 [처리절차]
-1. 시스템 프롬프트 및 단계별(규칙 보완, RAG 근거 요약, 3단계 위험도 판정, 대체문안 추천) 템플릿 DB 버전 관리
+1. 시스템 프롬프트 및 단계별(규칙 보완, RAG 근거 요약, 3단계 위험도 판정, 표준수정조항 추천) 템플릿 DB 버전 관리
 2. 비학습(Zero-Retention) 상용 LLM API(GPT-4o / Claude) 모델 라우팅 및 파라미터(Temperature 0.0~0.2) 설정
 3. 프롬프트 변경 시 골든셋 회귀 테스트 연동 검증
 [출력] 활성화된 프롬프트 체인 설정 및 버전별 실행 이력</t>
@@ -392,22 +392,22 @@
     <t>[F-15] 검토 품질 가드레일</t>
   </si>
   <si>
-    <t>LLM 응답의 정합성 검증, 식약처 필수 금지어 강제 차단(No-Downgrade), 타임아웃/폴백 및 토큰 비용 로깅을 전담합니다.
+    <t>LLM 응답의 정합성 검증, 공정위·표준원 필수 독소조항 강제 차단(No-Downgrade), 타임아웃/폴백 및 토큰 비용 로깅을 전담합니다.
 [처리절차]
-1. 1단계 확정 금지어 매칭 문장은 LLM이 임의로 '안전'으로 하향 판정하지 못하도록 가드레일(No-Downgrade) 강제 적용
+1. 1단계 확정 독소조항 매칭 문장은 LLM이 임의로 '안전'으로 하향 판정하지 못하도록 가드레일(No-Downgrade) 강제 적용
 2. JSON 스키마 유효성 검증 및 인용 법령 조항의 실제 RAG 존재 여부 교차 확인(환각 차단)
 3. 외부 LLM 응답 지연 시 지수 백오프 재시도 및 폴백 처리
 [출력] 검증 완료된 구조화 판정 결과 JSON 및 토큰 사용량/지연시간 감사 로그</t>
   </si>
   <si>
-    <t>[F-16] SyncGuard AI 1차 검토 자동 파이프라인</t>
-  </si>
-  <si>
-    <t>마케팅허브/포털 시안 및 동영상 캡처 장면 등록 시 파싱부터 3단계 판정·집계까지 비동기 작업 파이프라인을 총괄 오케스트레이션합니다.
+    <t>[F-16] SyncFlow AI 1차 검토 자동 파이프라인</t>
+  </si>
+  <si>
+    <t>전자구매포털/포털 계약·도서 및 설계도면 도면 스냅샷 등록 시 파싱부터 3단계 판정·집계까지 비동기 작업 파이프라인을 총괄 오케스트레이션합니다.
 [처리절차]
-1. 파이프라인 단계: 시안/스냅샷 수신 ➔ 문서·이미지 파싱(F-01/02) ➔ 문장 분리(F-03) ➔ 전성분 RDB·표현사전 룰 매칭(F-10) ➔ 식약처 법령·ProductLab 실증 RAG(F-07) ➔ 비학습 LLM 3단계 판정 및 대체문구 생성(F-11/12)
+1. 파이프라인 단계: 계약·도서/스냅샷 수신 ➔ 문서·이미지 파싱(F-01/02) ➔ 문장 분리(F-03) ➔ 자재BOM RDB·표현사전 룰 매칭(F-10) ➔ 공정위·표준원 법령·PLM-Nexus 시험검증 RAG(F-07) ➔ 비학습 LLM 3단계 판정 및 표준수정조항 생성(F-11/12)
 2. 장애 대응: Redis 작업 큐 기반 비동기 워커(AWS EC2) 분산 처리, 개별 문장 실패 시 최대 3회 자동 재시도 및 실시간 진행률(0~100%) 상태 제공
-[출력] 시안/동영상 전체 문장별 1차 AI 심의 결과 세트 및 종합 위험도 요약</t>
+[출력] 계약·도서/설계도면 전체 문장별 1차 AI 검증 결과 세트 및 종합 위험도 요약</t>
   </si>
   <si>
     <t>공통 및 기반 개발</t>
@@ -416,69 +416,69 @@
     <t>[F-17] 역할 기반 권한 관리 (RBAC)</t>
   </si>
   <si>
-    <t>마케터(본인/팀 시안 등록), 연구원(실증 검증), RA(최종 심의/승인), 관리자(전체 통제) 권한 격리.
-[처리절차] 마케터(본인/팀 시안 등록), 연구원(실증 검증), RA(최종 심의/승인), 관리자(전체 통제) 권한 격리.
+    <t>구매담당자(본인/팀 계약·도서 등록), 연구원(시험검증 검증), QA(최종 검증/승인), 관리자(전체 통제) 권한 격리.
+[처리절차] 구매담당자(본인/팀 계약·도서 등록), 연구원(시험검증 검증), QA(최종 검증/승인), 관리자(전체 통제) 권한 격리.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
     <t>[F-18] 인앱 및 이메일 알림 (Notification)</t>
   </si>
   <si>
-    <t>AI 1차 검토 완료, 실증자료 제출 요청, RA 배정/심의 완료 시 인앱 알림 및 이메일 전송.
-[처리절차] AI 1차 검토 완료, 실증자료 제출 요청, RA 배정/심의 완료 시 인앱 알림 및 이메일 전송.
+    <t>AI 1차 검토 완료, 시험성적서 제출 요청, QA 배정/검증 완료 시 인앱 알림 및 이메일 전송.
+[처리절차] AI 1차 검토 완료, 시험성적서 제출 요청, QA 배정/검증 완료 시 인앱 알림 및 이메일 전송.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
     <t>[F-19] 파일 및 스냅샷 업로드 공통 모듈 (AWS S3)</t>
   </si>
   <si>
-    <t>AWS S3 기반 PPTX/PDF/긴 JPG 이미지 및 동영상(MP4)·사용자 지정 캡처 스냅샷 업로드, Pre-signed URL 발급, 파일 해시(SHA-256) 무결성 검증을 수행합니다.
+    <t>AWS S3 기반 PPTX/PDF/긴 JPG 이미지 및 설계도면(CAD/PDF)·사용자 지정 스냅샷 스냅샷 업로드, Pre-signed URL 발급, 파일 해시(SHA-256) 무결성 검증을 수행합니다.
 [처리절차]
-1. 대용량 시안 및 동영상 멀티파트 업로드, 동영상 재생 중 캡처한 다중 장면 이미지(PNG/JPG) S3 버킷 암호화(AES-256) 저장
-2. 시안 원본 및 스냅샷별 SHA-256 해시 생성 및 Pre-signed URL 기반 보안 열람 제공
+1. 대용량 계약·도서 및 설계도면 멀티파트 업로드, 설계도면 재생 중 스냅샷한 다중 장면 이미지(PNG/JPG) S3 버킷 암호화(AES-256) 저장
+2. 계약·도서 원본 및 스냅샷별 SHA-256 해시 생성 및 Pre-signed URL 기반 보안 열람 제공
 [출력] S3 오브젝트 키, Pre-signed URL, 파일 무결성 해시값</t>
   </si>
   <si>
     <t>[F-20] 검토 요청 등록 API &amp; 화면</t>
   </si>
   <si>
-    <t>브랜드/제품/국가/매체/유형(사전검수, 정식의뢰) 선택, 파일 드래그앤드롭 업로드, 채번(`REQ-YYYYMMDD-XXXX`).
-[처리절차] 브랜드/제품/국가/매체/유형(사전검수, 정식의뢰) 선택, 파일 드래그앤드롭 업로드, 채번(`REQ-YYYYMMDD-XXXX`).
+    <t>사업본부/제품/국가/매체/유형(사전검수, 정식의뢰) 선택, 파일 드래그앤드롭 업로드, 채번(`REQ-YYYYMMDD-XXXX`).
+[처리절차] 사업본부/제품/국가/매체/유형(사전검수, 정식의뢰) 선택, 파일 드래그앤드롭 업로드, 채번(`REQ-YYYYMMDD-XXXX`).
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
     <t>[F-21] 요청 목록 및 상태 조회 API &amp; 화면</t>
   </si>
   <si>
-    <t>상태별(접수, AI검토중, RA검토중, 완료), 위험도별 필터링 및 페이징 목록.
-[처리절차] 상태별(접수, AI검토중, RA검토중, 완료), 위험도별 필터링 및 페이징 목록.
+    <t>상태별(접수, AI검토중, QA검토중, 완료), 위험도별 필터링 및 페이징 목록.
+[처리절차] 상태별(접수, AI검토중, QA검토중, 완료), 위험도별 필터링 및 페이징 목록.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
     <t>중</t>
   </si>
   <si>
-    <t>[F-22] 실증자료 요청 안내 (메일 발송)</t>
-  </si>
-  <si>
-    <t>실증 필요 문장 발생 시 담당 연구원에게 전용 웹 링크와 함께 제출 요청 메일 발송.
-[처리절차] 실증 필요 문장 발생 시 담당 연구원에게 전용 웹 링크와 함께 제출 요청 메일 발송.
+    <t>[F-22] 시험성적서 요청 안내 (메일 발송)</t>
+  </si>
+  <si>
+    <t>시험검증 필요 문장 발생 시 담당 연구원에게 전용 웹 링크와 함께 제출 요청 메일 발송.
+[처리절차] 시험검증 필요 문장 발생 시 담당 연구원에게 전용 웹 링크와 함께 제출 요청 메일 발송.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
     <t>[F-23] 검토 결과 리포트 생성 (PDF/Excel)</t>
   </si>
   <si>
-    <t>문장별 판정, 근거 법령, 대체 표현, 실증 매핑 정보를 포함한 공식 심의 리포트 다운로드.
-[처리절차] 문장별 판정, 근거 법령, 대체 표현, 실증 매핑 정보를 포함한 공식 심의 리포트 다운로드.
+    <t>문장별 판정, 근거 법령, 대체 표현, 시험검증 매핑 정보를 포함한 공식 검증 리포트 다운로드.
+[처리절차] 문장별 판정, 근거 법령, 대체 표현, 시험검증 매핑 정보를 포함한 공식 검증 리포트 다운로드.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
     <t>[F-24] 결과 통보</t>
   </si>
   <si>
-    <t>RA 심의 확정 시 요청자 및 유관부서에 리포트 다운로드 링크와 함께 최종 결과 자동 통보.
-[처리절차] RA 심의 확정 시 요청자 및 유관부서에 리포트 다운로드 링크와 함께 최종 결과 자동 통보.
+    <t>QA 검증 확정 시 요청자 및 유관부서에 리포트 다운로드 링크와 함께 최종 결과 자동 통보.
+[처리절차] QA 검증 확정 시 요청자 및 유관부서에 리포트 다운로드 링크와 함께 최종 결과 자동 통보.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
@@ -488,26 +488,26 @@
     <t>[F-25] 헤더 / GNB / 푸터 레이아웃</t>
   </si>
   <si>
-    <t>상단 로고, 글로벌 네비게이션(검토요청, 검토결과, 심의이력, 실증검증, 관리자), 사용자 역할 배지, 대외비 표기.
-[처리절차] 상단 로고, 글로벌 네비게이션(검토요청, 검토결과, 심의이력, 실증검증, 관리자), 사용자 역할 배지, 대외비 표기.
+    <t>상단 로고, 글로벌 네비게이션(검토요청, 검토결과, 검증이력, 시험검증검증, 관리자), 사용자 역할 배지, 대외비 표기.
+[처리절차] 상단 로고, 글로벌 네비게이션(검토요청, 검토결과, 검증이력, 시험검증검증, 관리자), 사용자 역할 배지, 대외비 표기.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
-    <t>[F-26] 검토 대상 문장 및 동영상 캡처 장면 편집기</t>
-  </si>
-  <si>
-    <t>시안 슬라이드/동영상 플레이어 미리보기와 추출된 장면·문장 목록 Side-by-Side 뷰, 사용자 지정 장면 캡처·삭제, 문장 병합 및 직접 수정을 지원합니다.
+    <t>[F-26] 검토 대상 문장 및 설계도면 도면 스냅샷 편집기</t>
+  </si>
+  <si>
+    <t>계약·도서 슬라이드/설계도면 플레이어 미리보기와 추출된 장면·문장 목록 Side-by-Side 뷰, 사용자 지정 장면 스냅샷·삭제, 문장 병합 및 직접 수정을 지원합니다.
 [처리절차]
-1. 동영상(MP4) 재생 중 심의가 필요한 주요 자막·연출 구간을 사용자가 클릭하여 다중 스냅샷 이미지로 캡처·저장
-2. 캡처된 장면 이미지 및 일반 시안에서 추출된 문장 목록을 좌우 대조 화면에 표시하고 오인식 문장 수동 교정 및 불필요 문구 제외 처리
-[출력] 정제 확정된 심의 대상 장면 이미지 및 문장 리스트</t>
-  </si>
-  <si>
-    <t>[F-27] 실증 검증 화면</t>
-  </si>
-  <si>
-    <t>AI가 실증 필요로 분류한 문장에 대해 연구원이 '확인완료/불필요' 판정하고 시험성적서 링크 및 페이지 메모 등록.
-[처리절차] AI가 실증 필요로 분류한 문장에 대해 연구원이 '확인완료/불필요' 판정하고 시험성적서 링크 및 페이지 메모 등록.
+1. 설계도면(CAD/PDF) 재생 중 검증이 필요한 주요 자막·연출 구간을 사용자가 클릭하여 다중 스냅샷 이미지로 스냅샷·저장
+2. 스냅샷된 장면 이미지 및 일반 계약·도서에서 추출된 문장 목록을 좌우 대조 화면에 표시하고 오인식 문장 수동 교정 및 불필요 조항 제외 처리
+[출력] 정제 확정된 검증 대상 장면 이미지 및 문장 리스트</t>
+  </si>
+  <si>
+    <t>[F-27] 시험검증 검증 화면</t>
+  </si>
+  <si>
+    <t>AI가 시험검증 필요로 분류한 문장에 대해 연구원이 '확인완료/불필요' 판정하고 시험성적서 링크 및 페이지 메모 등록.
+[처리절차] AI가 시험검증 필요로 분류한 문장에 대해 연구원이 '확인완료/불필요' 판정하고 시험성적서 링크 및 페이지 메모 등록.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
@@ -519,19 +519,19 @@
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
-    <t>[F-29] RA 최종 판정 입력 (피드백 UI)</t>
-  </si>
-  <si>
-    <t>RA 담당자가 AI 판정 승인/수정, 대체 표현 채택/직접 작성, 확정 Claim 입력, 일괄 승인 및 완료 처리.
-[처리절차] RA 담당자가 AI 판정 승인/수정, 대체 표현 채택/직접 작성, 확정 Claim 입력, 일괄 승인 및 완료 처리.
+    <t>[F-29] QA 최종 판정 입력 (피드백 UI)</t>
+  </si>
+  <si>
+    <t>법무·QA 담당자가 AI 판정 승인/수정, 대체 표현 채택/직접 작성, 확정 Spec 입력, 일괄 승인 및 완료 처리.
+[처리절차] 법무·QA 담당자가 AI 판정 승인/수정, 대체 표현 채택/직접 작성, 확정 Spec 입력, 일괄 승인 및 완료 처리.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
     <t>[F-30] 검토 이력 다차원 검색</t>
   </si>
   <si>
-    <t>표현 키워드, 제품, 브랜드, 기간, 판정 등급 및 시맨틱 유사 표현 검색, 과거 심의 타임라인 조회.
-[처리절차] 표현 키워드, 제품, 브랜드, 기간, 판정 등급 및 시맨틱 유사 표현 검색, 과거 심의 타임라인 조회.
+    <t>표현 키워드, 제품, 사업본부, 기간, 판정 등급 및 시맨틱 유사 표현 검색, 과거 검증 타임라인 조회.
+[처리절차] 표현 키워드, 제품, 사업본부, 기간, 판정 등급 및 시맨틱 유사 표현 검색, 과거 검증 타임라인 조회.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
@@ -541,32 +541,32 @@
     <t>[F-31] 오프라인 평가 파이프라인 (Benchmark Evaluation)</t>
   </si>
   <si>
-    <t>골든셋 대상 일괄 검토 실행, 정확도(Accuracy), 정밀도(Precision), 재현율(Recall), RA 일치율 자동 산출 및 버전 간 비교.
-[처리절차] 골든셋 대상 일괄 검토 실행, 정확도(Accuracy), 정밀도(Precision), 재현율(Recall), RA 일치율 자동 산출 및 버전 간 비교.
+    <t>골든셋 대상 일괄 검토 실행, 정확도(Accuracy), 정밀도(Precision), 재현율(Recall), QA 일치율 자동 산출 및 버전 간 비교.
+[처리절차] 골든셋 대상 일괄 검토 실행, 정확도(Accuracy), 정밀도(Precision), 재현율(Recall), QA 일치율 자동 산출 및 버전 간 비교.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
     <t>[F-32] 최종 검토 이력 DB (Immutable History)</t>
   </si>
   <si>
-    <t>RA 확정 시 원문, AI 판정, RA 최종 판정, 실증 링크, 심의자 메타를 불변 테이블에 영구 보존.
-[처리절차] RA 확정 시 원문, AI 판정, RA 최종 판정, 실증 링크, 심의자 메타를 불변 테이블에 영구 보존.
+    <t>QA 확정 시 원문, AI 판정, QA 최종 판정, 시험검증 링크, 검증자 메타를 불변 테이블에 영구 보존.
+[처리절차] QA 확정 시 원문, AI 판정, QA 최종 판정, 시험검증 링크, 검증자 메타를 불변 테이블에 영구 보존.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
     <t>[F-33] 피드백 반영 (승인 표현 &amp; Few-shot 갱신)</t>
   </si>
   <si>
-    <t>RA가 승인한 표현 및 확정 Claim을 표현 사전에 자동 등록하고 프롬프트 Few-shot 예시 풀에 반영.
-[처리절차] RA가 승인한 표현 및 확정 Claim을 표현 사전에 자동 등록하고 프롬프트 Few-shot 예시 풀에 반영.
+    <t>QA가 승인한 표현 및 확정 Spec을 표현 사전에 자동 등록하고 프롬프트 Few-shot 예시 풀에 반영.
+[처리절차] QA가 승인한 표현 및 확정 Spec을 표현 사전에 자동 등록하고 프롬프트 Few-shot 예시 풀에 반영.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
     <t>[F-34] 골든 평가셋 구축</t>
   </si>
   <si>
-    <t>대표적인 과거 심의 사례 및 엣지 케이스를 카테고리별로 균형 있게 선별하여 표준 평가셋(Golden Set) 버전 관리.
-[처리절차] 대표적인 과거 심의 사례 및 엣지 케이스를 카테고리별로 균형 있게 선별하여 표준 평가셋(Golden Set) 버전 관리.
+    <t>대표적인 과거 검증 사례 및 엣지 케이스를 카테고리별로 균형 있게 선별하여 표준 평가셋(Golden Set) 버전 관리.
+[처리절차] 대표적인 과거 검증 사례 및 엣지 케이스를 카테고리별로 균형 있게 선별하여 표준 평가셋(Golden Set) 버전 관리.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
@@ -581,25 +581,25 @@
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
-    <t>[F-36] 마케팅허브(MarketingHub) 양방향 API 연동</t>
-  </si>
-  <si>
-    <t>현업 주 접점인 마케팅허브에서 광고 시안·동영상 심의 의뢰를 수신하고, AI 사전 판정 대조 뷰어 링크 제공 및 RA 최종 확정 결과(PDF 리포트)를 웹훅/REST API로 회신합니다.
+    <t>[F-36] 전자구매포털(SRM-Portal) 양방향 API 연동</t>
+  </si>
+  <si>
+    <t>현업 주 접점인 전자구매포털에서 구매계약 계약·도서·설계도면 검증 요청를 수신하고, AI 사전 판정 대조 뷰어 링크 제공 및 QA 최종 확정 결과(PDF 리포트)를 웹훅/REST API로 회신합니다.
 [처리절차]
-1. [의뢰 수신] 마케팅허브 심의 신청 시 메타데이터(브랜드, 제품코드, 신청자) 및 첨부 시안/동영상 정보를 수신하여 자동 접수
-2. [뷰어 연동] 마케팅허브 화면 내 'AI 심의 결과 보기' 버튼 클릭 시 SSO 인증 연계된 Side-by-Side 대조 뷰어 호출
-3. [결과 회신] RA 최종 승인/조건부승인/반려 확정 시 판정 요약 및 의견서 PDF URL을 마케팅허브으로 즉시 송신(실패 시 큐 재시도)
-[출력] 마케팅허브 의뢰 매핑 번호, 대조 뷰어 SSO 딥링크, 최종 심의 결과 회신 전문</t>
-  </si>
-  <si>
-    <t>[F-37] 프로덕트랩(ProductLab) 실증·전성분 연계 및 [Option] KT 레몬 연동</t>
-  </si>
-  <si>
-    <t>프로덕트랩(ProductLab) 및 사내 전성분 RDB를 통해 제품 처방·배합한도·인체적용시험 실증보고서를 연동하며, KT 레몬 API는 [Option]으로 상용 LLM 파싱과 비교 검증 후 연계 여부를 결정합니다.
+1. [의뢰 수신] 전자구매포털 검증 신청 시 메타데이터(사업본부, 제품코드, 신청자) 및 첨부 계약·도서/설계도면 정보를 수신하여 자동 접수
+2. [뷰어 연동] 전자구매포털 화면 내 'AI 검증 결과 보기' 버튼 클릭 시 SSO 인증 연계된 Side-by-Side 대조 뷰어 호출
+3. [결과 회신] QA 최종 승인/조건부승인/반려 확정 시 판정 요약 및 의견서 PDF URL을 전자구매포털으로 즉시 송신(실패 시 큐 재시도)
+[출력] 전자구매포털 의뢰 매핑 번호, 대조 뷰어 SSO 딥링크, 최종 검증 결과 회신 전문</t>
+  </si>
+  <si>
+    <t>[F-37] 피엘엠넥서스(PLM-Nexus) 시험검증·자재BOM 연계 및 [Option] HB-Monitor 연동</t>
+  </si>
+  <si>
+    <t>피엘엠넥서스(PLM-Nexus) 및 사내 자재BOM RDB를 통해 제품 설계사양·유해물질한도·공인신뢰성시험 시험검증보고서를 연동하며, HB-Monitor API는 [Option]으로 상용 LLM 파싱과 비교 검증 후 연계 여부를 결정합니다.
 [처리절차]
-1. [필수] 제품코드 기준 사내 전성분 RDB 및 ProductLab 원료 규격·배합한도·인체적용시험/세포효능 실증 데이터 조회 및 교차 검증
-2. [Option] R&amp;I 연구보고서 벡터 데이터(KT 레몬) API 호출 방식과 상용 LLM(Claude/GPT) 원문 직접 파싱 방식의 정확도·속도 비교 PoC 수행 후 최적 연계 방식 적용
-[출력] 전성분 배합규격 적합 여부, 매핑된 실증 시험성적서 메타/문구, [Option] 벡터 검색 결과</t>
+1. [필수] 제품코드 기준 사내 자재BOM RDB 및 PLM-Nexus 원소재 규격·유해물질한도·공인신뢰성시험/배상한도성능규격 시험검증 데이터 조회 및 교차 검증
+2. [Option] 선행연구소 연구보고서 벡터 데이터(HB-Monitor) API 호출 방식과 상용 LLM(Claude/GPT) 원문 직접 파싱 방식의 정확도·속도 비교 PoC 수행 후 최적 연계 방식 적용
+[출력] 자재BOM 조성규격 적합 여부, 매핑된 시험검증 시험성적서 메타/조항, [Option] 벡터 검색 결과</t>
   </si>
   <si>
     <t>관리자 및 운영</t>
@@ -608,16 +608,16 @@
     <t>[F-38] 사용자 및 권한 관리</t>
   </si>
   <si>
-    <t>SSO 사용자 목록 동기화, 브랜드/부서 배정, 역할 부여, 계정 비활성화, 권한 변경 감사 로그.
-[처리절차] SSO 사용자 목록 동기화, 브랜드/부서 배정, 역할 부여, 계정 비활성화, 권한 변경 감사 로그.
+    <t>SSO 사용자 목록 동기화, 사업본부/부서 배정, 역할 부여, 계정 비활성화, 권한 변경 감사 로그.
+[처리절차] SSO 사용자 목록 동기화, 사업본부/부서 배정, 역할 부여, 계정 비활성화, 권한 변경 감사 로그.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
     <t>[F-39] 규제 DB 관리</t>
   </si>
   <si>
-    <t>식약처 가이드라인 등록/개정/폐기, 청킹 미리보기, RAG 임베딩 재인덱싱 트리거 및 진행률 모니터링.
-[처리절차] 식약처 가이드라인 등록/개정/폐기, 청킹 미리보기, RAG 임베딩 재인덱싱 트리거 및 진행률 모니터링.
+    <t>공정위·표준원 가이드라인 등록/개정/폐기, 청킹 미리보기, RAG 임베딩 재인덱싱 트리거 및 진행률 모니터링.
+[처리절차] 공정위·표준원 가이드라인 등록/개정/폐기, 청킹 미리보기, RAG 임베딩 재인덱싱 트리거 및 진행률 모니터링.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
@@ -640,16 +640,16 @@
     <t>[F-42] 운영 지표 대시보드</t>
   </si>
   <si>
-    <t>기간별 검토 건수, 위험 등급 분포 차트, AI-RA 일치율 추이, LLM 토큰 사용량 및 비용 분석.
-[처리절차] 기간별 검토 건수, 위험 등급 분포 차트, AI-RA 일치율 추이, LLM 토큰 사용량 및 비용 분석.
+    <t>기간별 검토 건수, 위험 등급 분포 차트, AI-QA 일치율 추이, LLM 토큰 사용량 및 비용 분석.
+[처리절차] 기간별 검토 건수, 위험 등급 분포 차트, AI-QA 일치율 추이, LLM 토큰 사용량 및 비용 분석.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
     <t>[F-43] 공통 코드 관리</t>
   </si>
   <si>
-    <t>브랜드, 제품 카테고리, 광고 매체, 실증 유형, 심의 카테고리 코드 관리 및 사용 중 코드 삭제 방지.
-[처리절차] 브랜드, 제품 카테고리, 광고 매체, 실증 유형, 심의 카테고리 코드 관리 및 사용 중 코드 삭제 방지.
+    <t>사업본부, 제품 카테고리, 구매계약 매체, 시험검증 유형, 검증 카테고리 코드 관리 및 사용 중 코드 삭제 방지.
+[처리절차] 사업본부, 제품 카테고리, 구매계약 매체, 시험검증 유형, 검증 카테고리 코드 관리 및 사용 중 코드 삭제 방지.
 [출력] 처리 결과 및 DB 반영</t>
   </si>
   <si>
@@ -728,7 +728,7 @@
     <t>품질특성</t>
   </si>
   <si>
-    <t xml:space="preserve">     □기능성   □ 비기능성 (□신뢰성 □성능 □사용성 □효율성 □유지보수성 □이식성 □기타)</t>
+    <t xml:space="preserve">     □핵심규격   □ 비핵심규격 (□신뢰성 □성능 □사용성 □효율성 □유지보수성 □이식성 □기타)</t>
   </si>
   <si>
     <t>3. 요구사항 변경내역</t>
